--- a/data/trans_bre/IP1019-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1019-Edad-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,88</t>
+          <t>-0,78; 0,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,33</t>
+          <t>-0,19; 0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
